--- a/artfynd/A 42309-2021 artfynd.xlsx
+++ b/artfynd/A 42309-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42309-2021 artfynd.xlsx
+++ b/artfynd/A 42309-2021 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>66553440</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505375.0564455764</v>
+        <v>505375</v>
       </c>
       <c r="R10" t="n">
-        <v>6931899.721650532</v>
+        <v>6931900</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1679,19 +1679,9 @@
           <t>2015-06-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2015-06-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 42309-2021 artfynd.xlsx
+++ b/artfynd/A 42309-2021 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>66553440</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 42309-2021 artfynd.xlsx
+++ b/artfynd/A 42309-2021 artfynd.xlsx
@@ -1609,7 +1609,7 @@
         <v>66553440</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 42309-2021 artfynd.xlsx
+++ b/artfynd/A 42309-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553432</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97062133</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553436</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553446</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60950270</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553437</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553443</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553447</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553452</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54872458</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553439</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553444</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553453</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2204,6 +2279,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553441</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2306,6 +2386,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553433</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2408,6 +2493,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553434</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,6 +2600,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553438</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2617,8 +2712,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66553440</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>